--- a/output/usb_pd_validation_report.xlsx
+++ b/output/usb_pd_validation_report.xlsx
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Section 1.1 at position 1, expected 0', 'Section 1.2 at position 2, expected 1', 'Section 1.2.1 at position 3, expected 2', 'Section 1.3 at position 4, expected 3', 'Section 1.4 at position 5, expected 4', 'Section 1.4.1 at position 6, expected 5', 'Section 1.4.2 at position 7, expected 6', 'Section 1.4.3 at position 8, expected 7', 'Section 1.5 at position 9, expected 8', 'Section 1.6 at position 10, expected 9', 'Section 1.7 at position 11, expected 10', 'Section 2.1 at position 12, expected 11', 'Section 2.1.1 at position 13, expected 12', 'Section 2.1.2 at position 14, expected 13', 'Section 2.1.3 at position 15, expected 14', 'Section 2.3 at position 16, expected 15', 'Section 2.4 at position 17, expected 16', 'Section 2.4.1 at position 18, expected 17', 'Section 2.4.2 at position 19, expected 18', 'Section 2.4.3 at position 20, expected 19', 'Section 2.4.4 at position 21, expected 20', 'Section 2.5 at position 22, expected 21', 'Section 2.5.1 at position 23, expected 22', 'Section 2.5.2 at position 24, expected 23', 'Section 2.5.3 at position 25, expected 24', 'Section 2.6 at position 26, expected 25', 'Section 2.6.1 at position 27, expected 26', 'Section 2.6.2 at position 28, expected 27', 'Section 2.6.3 at position 29, expected 28', 'Section 2.6.4 at position 30, expected 29', 'Section 2.6.5 at position 31, expected 30', 'Section 2.6.6 at position 32, expected 31', 'Section 2.6.7 at position 33, expected 32', 'Section 2.6.8 at position 34, expected 33', 'Section 2.7 at position 35, expected 34', 'Section 2.8 at position 36, expected 35', 'Section 2.8.1 at position 37, expected 36', 'Section 2.8.2 at position 38, expected 37', 'Section 2.8.3 at position 39, expected 38', 'Section 4.1 at position 40, expected 39', 'Section 4.2 at position 41, expected 40', 'Section 4.3 at position 42, expected 41', 'Section 4.4 at position 43, expected 42', 'Section 5.1 at position 44, expected 43', 'Section 5.2 at position 45, expected 44', 'Section 5.3 at position 46, expected 45', 'Section 5.4 at position 47, expected 46', 'Section 5.5 at position 48, expected 47', 'Section 5.6 at position 49, expected 48', 'Section 5.6.1 at position 50, expected 49', 'Section 5.6.2 at position 51, expected 50', 'Section 5.6.3 at position 52, expected 51', 'Section 5.6.4 at position 53, expected 52', 'Section 5.6.5 at position 54, expected 53', 'Section 5.7 at position 55, expected 54', 'Section 5.8 at position 56, expected 55', 'Section 5.8.1 at position 57, expected 56', 'Section 5.8.2 at position 58, expected 57', 'Section 5.8.3 at position 59, expected 58', 'Section 5.8.4 at position 60, expected 59', 'Section 5.8.5 at position 61, expected 60', 'Section 5.8.6 at position 62, expected 61', 'Section 5.9 at position 63, expected 62', 'Section 5.9.1 at position 64, expected 63', 'Section 5.9.2 at position 65, expected 64', 'Section 6 at position 66, expected 65', 'Section 6.1 at position 67, expected 66', 'Section 6.2 at position 68, expected 67', 'Section 6.2.1 at position 69, expected 68', 'Section 6.3 at position 70, expected 69', 'Section 6.3.1 at position 71, expected 70', 'Section 6.3.2 at position 72, expected 71', 'Section 6.3.3 at position 73, expected 72', 'Section 6.3.4 at position 74, expected 73', 'Section 6.3.5 at position 75, expected 74', 'Section 6.3.6 at position 76, expected 75', 'Section 6.3.7 at position 78, expected 76', 'Section 6.3.8 at position 79, expected 77', 'Section 6.3.9 at position 80, expected 78', 'Section 6.3.10 at position 77, expected 79', 'Section 6.3.11 at position 81, expected 80', 'Section 6.3.12 at position 82, expected 81', 'Section 6.3.13 at position 83, expected 82', 'Section 6.3.14 at position 84, expected 83', 'Section 6.3.15 at position 85, expected 84', 'Section 6.3.16 at position 86, expected 85', 'Section 6.3.17 at position 87, expected 86', 'Section 6.3.18 at position 88, expected 87', 'Section 6.3.19 at position 89, expected 88', 'Section 6.3.20 at position 90, expected 89', 'Section 6.3.21 at position 91, expected 90', 'Section 6.3.22 at position 92, expected 91', 'Section 6.3.23 at position 93, expected 92', 'Section 6.4 at position 94, expected 93', 'Section 6.4.1 at position 95, expected 94', 'Section 6.4.2 at position 96, expected 95', 'Section 6.4.3 at position 97, expected 96', 'Section 6.4.4 at position 98, expected 97', 'Section 6.4.5 at position 99, expected 98', 'Section 6.4.6 at position 100, expected 99', 'Section 6.4.7 at position 101, expected 100', 'Section 6.4.8 at position 102, expected 101', 'Section 6.4.9 at position 103, expected 102', 'Section 6.4.10 at position 104, expected 103', 'Section 6.4.11 at position 105, expected 104', 'Section 6.5 at position 106, expected 105', 'Section 6.5.1 at position 107, expected 106', 'Section 6.5.2 at position 108, expected 107', 'Section 6.5.3 at position 109, expected 108', 'Section 6.5.4 at position 110, expected 109', 'Section 6.5.5 at position 111, expected 110', 'Section 6.5.6 at position 112, expected 111', 'Section 6.5.7 at position 113, expected 112', 'Section 6.5.8 at position 114, expected 113', 'Section 6.5.9 at position 115, expected 114', 'Section 6.5.10 at position 116, expected 115', 'Section 6.5.11 at position 117, expected 116', 'Section 6.5.12 at position 118, expected 117', 'Section 6.5.13 at position 119, expected 118', 'Section 6.5.14 at position 120, expected 119', 'Section 6.5.15 at position 121, expected 120', 'Section 6.5.16 at position 122, expected 121', 'Section 6.6 at position 123, expected 122', 'Section 6.6.1 at position 124, expected 123', 'Section 6.6.2 at position 125, expected 124', 'Section 6.6.3 at position 126, expected 125', 'Section 6.6.4 at position 127, expected 126', 'Section 6.6.5 at position 128, expected 127', 'Section 6.6.6 at position 129, expected 128', 'Section 6.6.7 at position 130, expected 129', 'Section 6.6.8 at position 132, expected 130', 'Section 6.6.9 at position 133, expected 131', 'Section 6.6.10 at position 131, expected 132', 'Section 6.6.11 at position 134, expected 133', 'Section 6.6.12 at position 135, expected 134', 'Section 6.6.13 at position 136, expected 135', 'Section 6.6.14 at position 137, expected 136', 'Section 6.6.15 at position 138, expected 137', 'Section 6.6.16 at position 139, expected 138', 'Section 6.6.17 at position 140, expected 139', 'Section 6.6.18 at position 141, expected 140', 'Section 6.6.19 at position 142, expected 141', 'Section 6.6.20 at position 143, expected 142', 'Section 6.6.21 at position 144, expected 143', 'Section 6.6.22 at position 145, expected 144', 'Section 6.7 at position 146, expected 145', 'Section 6.7.1 at position 147, expected 146', 'Section 6.7.2 at position 148, expected 147', 'Section 6.7.3 at position 149, expected 148', 'Section 6.7.4 at position 150, expected 149', 'Section 6.7.5 at position 151, expected 150', 'Section 6.7.6 at position 152, expected 151', 'Section 6.7.7 at position 153, expected 152', 'Section 6.8 at position 154, expected 153', 'Section 6.8.1 at position 155, expected 154', 'Section 6.8.2 at position 156, expected 155', 'Section 6.8.3 at position 157, expected 156', 'Section 6.8.4 at position 158, expected 157', 'Section 6.9 at position 159, expected 158', 'Section 6.10 at position 160, expected 159', 'Section 6.11 at position 161, expected 160', 'Section 6.12 at position 162, expected 161', 'Section 6.12.1 at position 163, expected 162', 'Section 6.12.2 at position 164, expected 163', 'Section 6.12.3 at position 165, expected 164', 'Section 6.13 at position 166, expected 165', 'Section 6.13.1 at position 167, expected 166', 'Section 6.13.2 at position 168, expected 167', 'Section 6.13.3 at position 169, expected 168', 'Section 6.13.4 at position 170, expected 169', 'Section 6.13.5 at position 171, expected 170', 'Section 6.13.6 at position 172, expected 171', 'Section 6.13.7 at position 173, expected 172', 'Section 6.14 at position 174, expected 173', 'Section 7 at position 175, expected 174', 'Section 7.1 at position 176, expected 175', 'Section 7.1.1 at position 177, expected 176', 'Section 7.1.2 at position 178, expected 177', 'Section 7.1.3 at position 179, expected 178', 'Section 7.1.4 at position 180, expected 179', 'Section 7.1.5 at position 181, expected 180', 'Section 7.1.6 at position 182, expected 181', 'Section 7.1.7 at position 183, expected 182', 'Section 7.1.8 at position 184, expected 183', 'Section 7.1.9 at position 187, expected 184', 'Section 7.1.12 at position 188, expected 187', 'Section 7.1.13 at position 189, expected 188', 'Section 7.1.14 at position 190, expected 189', 'Section 7.1.15 at position 191, expected 190', 'Section 7.2 at position 192, expected 191', 'Section 7.2.1 at position 193, expected 192', 'Section 7.2.2 at position 194, expected 193', 'Section 7.2.3 at position 195, expected 194', 'Section 7.2.4 at position 196, expected 195', 'Section 7.2.5 at position 197, expected 196', 'Section 7.2.6 at position 198, expected 197', 'Section 7.2.7 at position 199, expected 198', 'Section 7.2.8 at position 200, expected 199', 'Section 7.2.9 at position 201, expected 200', 'Section 7.2.10 at position 202, expected 201', 'Section 7.3 at position 203, expected 202', 'Section 7.3.1 at position 204, expected 203', 'Section 7.3.2 at position 205, expected 204', 'Section 7.3.3 at position 206, expected 205', 'Section 7.3.4 at position 207, expected 206', 'Section 7.4 at position 208, expected 207', 'Section 7.4.1 at position 209, expected 208', 'Section 7.4.2 at position 210, expected 209', 'Section 7.4.3 at position 211, expected 210', 'Section 8 at position 212, expected 211', 'Section 8.1 at position 213, expected 212', 'Section 8.2 at position 214, expected 213', 'Section 8.2.1 at position 215, expected 214', 'Section 8.2.2 at position 216, expected 215', 'Section 8.2.3 at position 217, expected 216', 'Section 8.2.4 at position 218, expected 217', 'Section 8.2.5 at position 219, expected 218', 'Section 8.2.6 at position 220, expected 219', 'Section 8.2.7 at position 221, expected 220', 'Section 8.3 at position 222, expected 221', 'Section 8.3.1 at position 223, expected 222', 'Section 8.3.2 at position 224, expected 223', 'Section 8.3.3 at position 225, expected 224', 'Section 9 at position 226, expected 225', 'Section 9.1 at position 227, expected 226', 'Section 9.1.1 at position 228, expected 227', 'Section 9.1.2 at position 229, expected 228', 'Section 9.1.3 at position 230, expected 229', 'Section 9.1.4 at position 231, expected 230', 'Section 9.2 at position 232, expected 231', 'Section 9.2.1 at position 233, expected 232', 'Section 9.2.2 at position 234, expected 233', 'Section 9.2.3 at position 235, expected 234', 'Section 9.2.4 at position 236, expected 235', 'Section 9.3 at position 237, expected 236', 'Section 9.3.1 at position 238, expected 237', 'Section 9.4 at position 239, expected 238', 'Section 9.4.1 at position 240, expected 239', 'Section 9.4.2 at position 241, expected 240', 'Section 10 at position 0, expected 241']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>7530.236</v>
+        <v>14193.34</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7875,117 +7875,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UPnoivweresarl SReurilael sB u. s. P. o. w. e. r. D. .e l.i v. e. r.y . S.p .e .c i.f i. c.a .t i.o .n ., R. .e v. i.s i.o .n . 3. ..2 ., V. e. r.s .i o. n. 1. ..1 ., 2. 0. 2. 4. -.1 .0 . . . . . 9P9a5ge</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>127067</v>
+        <v>4404</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>8663</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4404</v>
+        <v>3319</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>719</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3319</v>
+        <v>0</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Section Overview</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2356</v>
       </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Section Overview</t>
+          <t>Conventions</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2356</v>
+        <v>0</v>
       </c>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conventions</t>
+          <t>Precedence</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8001,138 +8001,138 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Precedence</t>
+          <t>Keywords</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2899</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.4.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keywords</t>
+          <t>Numbering</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2899</v>
+        <v>1780</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>446</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Numbering</t>
+          <t>Related Documents</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1780</v>
+        <v>2381</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Related Documents</t>
+          <t>Terms and Abbreviations</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2381</v>
+        <v>42734</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>282</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Terms and Abbreviations</t>
+          <t>Parameter Values</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>42734</v>
+        <v>2751</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>7380</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Parameter Values</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2751</v>
+        <v>0</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Power Delivery Source Operational Contracts</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -8148,96 +8148,96 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Power Delivery Source Operational Contracts</t>
+          <t>Power Delivery Contract Negotiation</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3860</v>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Power Delivery Contract Negotiation</t>
+          <t>Other Uses for Power Delivery</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3860</v>
+        <v>3230</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>624</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other Uses for Power Delivery</t>
+          <t>USB Power Delivery Capable Devices</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3230</v>
+        <v>3209</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>556</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USB Power Delivery Capable Devices</t>
+          <t>SOP* Communication</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3209</v>
+        <v>0</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOP* Communication</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -8253,12 +8253,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>SOP* Collision Avoidance</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -8274,12 +8274,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOP* Collision Avoidance</t>
+          <t>SOP Communication</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -8295,264 +8295,264 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>2.4.4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOP Communication</t>
+          <t>SOP'/SOP'' Communication with Cable Plugs</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>4708</v>
       </c>
       <c r="D22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2.4.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SOP'/SOP'' Communication with Cable Plugs</t>
+          <t>Operational Overview</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4708</v>
+        <v>0</v>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Overview</t>
+          <t>Source Operation</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>8405</v>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Source Operation</t>
+          <t>Sink Operation</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8405</v>
+        <v>7432</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1464</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.5.3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sink Operation</t>
+          <t>Cable Plugs</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7432</v>
+        <v>952</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2.5.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cable Plugs</t>
+          <t>Architectural Overview</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>952</v>
+        <v>3560</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>165</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Architectural Overview</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3560</v>
+        <v>2492</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>561</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2.6.1</t>
+          <t>2.6.2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Message Formation and Transmission</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2492</v>
+        <v>0</v>
       </c>
       <c r="D29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2.6.2</t>
+          <t>2.6.3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Message Formation and Transmission</t>
+          <t>Collision Avoidance</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3668</v>
       </c>
       <c r="D30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2.6.3</t>
+          <t>2.6.4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Collision Avoidance</t>
+          <t>Power supply</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3668</v>
+        <v>0</v>
       </c>
       <c r="D31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2.6.4</t>
+          <t>2.6.5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Power supply</t>
+          <t>DFP/UFP</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2903</v>
       </c>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>541</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2.6.5</t>
+          <t>2.6.6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DFP/UFP</t>
+          <t>Cable and Connectors</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2903</v>
+        <v>0</v>
       </c>
       <c r="D33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2.6.6</t>
+          <t>2.6.7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cable and Connectors</t>
+          <t>Interactions between Non-PD, BC, and PD devices</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8568,75 +8568,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2.6.7</t>
+          <t>2.6.8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Interactions between Non-PD, BC, and PD devices</t>
+          <t>Power Rules</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2045</v>
       </c>
       <c r="D35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2.6.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Power Rules</t>
+          <t>Extended Power Range (EPR) Operation</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2045</v>
+        <v>4011</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Extended Power Range (EPR) Operation</t>
+          <t>Charging Models</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="D37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.8.1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charging Models</t>
+          <t>Fixed Supply Charging Models</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -8652,75 +8652,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2.8.1</t>
+          <t>2.8.2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fixed Supply Charging Models</t>
+          <t>Programmable Power Supply (PPS) Charging Models</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1734</v>
       </c>
       <c r="D39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2.8.2</t>
+          <t>2.8.3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Programmable Power Supply (PPS) Charging Models</t>
+          <t>Adjustable Voltage Supply (AVS) Charging Models</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1734</v>
+        <v>1160</v>
       </c>
       <c r="D40" t="b">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2.8.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adjustable Voltage Supply (AVS) Charging Models</t>
+          <t>Interoperability with other USB Specifications</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1160</v>
+        <v>0</v>
       </c>
       <c r="D41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Interoperability with other USB Specifications</t>
+          <t>Dead Battery Detection / Unpowered Port Detection</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -8736,12 +8736,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dead Battery Detection / Unpowered Port Detection</t>
+          <t>Cable IR Ground Drop (IR Drop)</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -8757,453 +8757,453 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cable IR Ground Drop (IR Drop)</t>
+          <t>Cable Type Detection</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3139</v>
       </c>
       <c r="D44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cable Type Detection</t>
+          <t>Physical Layer Overview</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3139</v>
+        <v>0</v>
       </c>
       <c r="D45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Physical Layer Overview</t>
+          <t>Physical Layer Functions</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="D46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Physical Layer Functions</t>
+          <t>Symbol Encoding</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1196</v>
+        <v>1600</v>
       </c>
       <c r="D47" t="b">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>199</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Symbol Encoding</t>
+          <t>Ordered Sets</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1600</v>
+        <v>1859</v>
       </c>
       <c r="D48" t="b">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ordered Sets</t>
+          <t>Transmitted Bit Ordering</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1859</v>
+        <v>618</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>309</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Transmitted Bit Ordering</t>
+          <t>Packet Format</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="D50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.6.1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Packet Format</t>
+          <t>Packet Framing</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>5089</v>
       </c>
       <c r="D51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>869</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5.6.1</t>
+          <t>5.6.2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Packet Framing</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5089</v>
+        <v>3031</v>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>869</v>
+        <v>570</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5.6.2</t>
+          <t>5.6.3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CRC</t>
+          <t>Packet Detection Errors</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3031</v>
+        <v>0</v>
       </c>
       <c r="D53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5.6.3</t>
+          <t>5.6.4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Packet Detection Errors</t>
+          <t>Hard Reset</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2359</v>
       </c>
       <c r="D54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5.6.4</t>
+          <t>5.6.5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hard Reset</t>
+          <t>Cable Reset</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2359</v>
+        <v>1034</v>
       </c>
       <c r="D55" t="b">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>393</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5.6.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cable Reset</t>
+          <t>Collision Avoidance</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1034</v>
+        <v>2123</v>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>175</v>
+        <v>349</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Collision Avoidance</t>
+          <t>Bi-phase Mark Coding (BMC) Signaling Scheme</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2123</v>
+        <v>0</v>
       </c>
       <c r="D57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.8.1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bi-phase Mark Coding (BMC) Signaling Scheme</t>
+          <t>Encoding and signaling</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>6219</v>
       </c>
       <c r="D58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5.8.1</t>
+          <t>5.8.2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Encoding and signaling</t>
+          <t>Transmit and Receive Masks</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6219</v>
+        <v>7173</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1095</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5.8.2</t>
+          <t>5.8.3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Transmit and Receive Masks</t>
+          <t>Transmitter Load Model</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7173</v>
+        <v>2091</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>1329</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5.8.3</t>
+          <t>5.8.4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Transmitter Load Model</t>
+          <t>BMC Common specifications</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2091</v>
+        <v>760</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>348</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5.8.4</t>
+          <t>5.8.5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BMC Common specifications</t>
+          <t>BMC Transmitter Specifications</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>760</v>
+        <v>7281</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>125</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5.8.5</t>
+          <t>5.8.6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BMC Transmitter Specifications</t>
+          <t>BMC Receiver Specifications</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7281</v>
+        <v>6655</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>1224</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5.8.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BMC Receiver Specifications</t>
+          <t>Built in Self-Test (BIST)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6655</v>
+        <v>0</v>
       </c>
       <c r="D64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.9.1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Built in Self-Test (BIST)</t>
+          <t>BIST Carrier Mode</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -9219,159 +9219,159 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5.9.1</t>
+          <t>5.9.2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BIST Carrier Mode</t>
+          <t>BIST Test Data Mode</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1376</v>
       </c>
       <c r="D66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5.9.2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BIST Test Data Mode</t>
+          <t>Protocol Layer . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1376</v>
+        <v>0</v>
       </c>
       <c r="D67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Protocol Layer . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="D68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Messages</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="D69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.2.1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Messages</t>
+          <t>Message Construction</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>29933</v>
       </c>
       <c r="D70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>5405</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6.2.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Message Construction</t>
+          <t>Control Message</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>29933</v>
+        <v>2802</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5405</v>
+        <v>502</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.3.1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Control Message</t>
+          <t>GoodCRC Message</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2802</v>
+        <v>0</v>
       </c>
       <c r="D72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>6.3.2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GoodCRC Message</t>
+          <t>GotoMin Message (Deprecated)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -9387,12 +9387,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6.3.2</t>
+          <t>6.3.3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GotoMin Message (Deprecated)</t>
+          <t>Accept Message</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -9408,96 +9408,96 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6.3.3</t>
+          <t>6.3.4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Accept Message</t>
+          <t>Reject Message</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2840</v>
       </c>
       <c r="D75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6.3.4</t>
+          <t>6.3.5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Reject Message</t>
+          <t>Ping Message</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2840</v>
+        <v>0</v>
       </c>
       <c r="D76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6.3.5</t>
+          <t>6.3.6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ping Message</t>
+          <t>PS_RDY Message</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2667</v>
       </c>
       <c r="D77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6.3.6</t>
+          <t>6.3.7</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PS_RDY Message</t>
+          <t>Get_Source_Cap Message</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2667</v>
+        <v>0</v>
       </c>
       <c r="D78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6.3.10</t>
+          <t>6.3.8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PR_Swap Message</t>
+          <t>Get_Sink_Cap Message</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -9513,12 +9513,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6.3.7</t>
+          <t>6.3.9</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Get_Source_Cap Message</t>
+          <t>DR_Swap Message</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -9534,117 +9534,117 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6.3.8</t>
+          <t>6.3.10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Get_Sink_Cap Message</t>
+          <t>PR_Swap Message</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>3741</v>
       </c>
       <c r="D81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>633</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6.3.9</t>
+          <t>6.3.11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DR_Swap Message</t>
+          <t>VCONN_Swap Message</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3741</v>
+        <v>3589</v>
       </c>
       <c r="D82" t="b">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>633</v>
+        <v>663</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6.3.11</t>
+          <t>6.3.12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VCONN_Swap Message</t>
+          <t>Wait Message</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3589</v>
+        <v>3479</v>
       </c>
       <c r="D83" t="b">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6.3.12</t>
+          <t>6.3.13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wait Message</t>
+          <t>Soft Reset Message</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3479</v>
+        <v>4252</v>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>628</v>
+        <v>679</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6.3.13</t>
+          <t>6.3.14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Soft Reset Message</t>
+          <t>Data_Reset Message</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4252</v>
+        <v>0</v>
       </c>
       <c r="D85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6.3.14</t>
+          <t>6.3.15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Data_Reset Message</t>
+          <t>Data_Reset_Complete Message</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -9660,54 +9660,54 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6.3.15</t>
+          <t>6.3.16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Data_Reset_Complete Message</t>
+          <t>Not_Supported Message</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>2786</v>
       </c>
       <c r="D87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6.3.16</t>
+          <t>6.3.17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Not_Supported Message</t>
+          <t>Get_Source_Cap_Extended Message</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2786</v>
+        <v>0</v>
       </c>
       <c r="D88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6.3.17</t>
+          <t>6.3.18</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Get_Source_Cap_Extended Message</t>
+          <t>Get_Status Message</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -9723,54 +9723,54 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6.3.18</t>
+          <t>6.3.19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Get_Status Message</t>
+          <t>FR_Swap Message</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>3525</v>
       </c>
       <c r="D90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6.3.19</t>
+          <t>6.3.20</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FR_Swap Message</t>
+          <t>Get_PPS_Status</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3525</v>
+        <v>0</v>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6.3.20</t>
+          <t>6.3.21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Get_PPS_Status</t>
+          <t>Get_Country_Codes</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -9786,12 +9786,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6.3.21</t>
+          <t>6.3.22</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Get_Country_Codes</t>
+          <t>Get_Sink_Cap_Extended Message</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -9807,541 +9807,541 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6.3.22</t>
+          <t>6.3.23</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Get_Sink_Cap_Extended Message</t>
+          <t>Get_Source_Info Message</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1756</v>
       </c>
       <c r="D94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6.3.23</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Get_Source_Info Message</t>
+          <t>Data Message</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1756</v>
+        <v>2487</v>
       </c>
       <c r="D95" t="b">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>255</v>
+        <v>423</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.4.1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Data Message</t>
+          <t>Capabilities Message</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2487</v>
+        <v>39013</v>
       </c>
       <c r="D96" t="b">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>423</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6.4.1</t>
+          <t>6.4.2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capabilities Message</t>
+          <t>Request Message</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>39013</v>
+        <v>12121</v>
       </c>
       <c r="D97" t="b">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>6406</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6.4.2</t>
+          <t>6.4.3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Request Message</t>
+          <t>BIST Message</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12121</v>
+        <v>7917</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>1928</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6.4.3</t>
+          <t>6.4.4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BIST Message</t>
+          <t>Vendor Defined Message</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7917</v>
+        <v>71928</v>
       </c>
       <c r="D99" t="b">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1370</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6.4.4</t>
+          <t>6.4.5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Vendor Defined Message</t>
+          <t>Battery_Status Message</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>71928</v>
+        <v>3086</v>
       </c>
       <c r="D100" t="b">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>12495</v>
+        <v>479</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6.4.5</t>
+          <t>6.4.6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Battery_Status Message</t>
+          <t>Alert Message</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3086</v>
+        <v>6875</v>
       </c>
       <c r="D101" t="b">
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>479</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6.4.6</t>
+          <t>6.4.7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alert Message</t>
+          <t>Get_Country_Info Message</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6875</v>
+        <v>911</v>
       </c>
       <c r="D102" t="b">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>1161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6.4.7</t>
+          <t>6.4.8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Get_Country_Info Message</t>
+          <t>Enter_USB Message</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>911</v>
+        <v>5556</v>
       </c>
       <c r="D103" t="b">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>135</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6.4.8</t>
+          <t>6.4.9</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Enter_USB Message</t>
+          <t>EPR_Request Message</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5556</v>
+        <v>1562</v>
       </c>
       <c r="D104" t="b">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>1011</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6.4.9</t>
+          <t>6.4.10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPR_Request Message</t>
+          <t>EPR_Mode Message</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1562</v>
+        <v>11474</v>
       </c>
       <c r="D105" t="b">
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>246</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6.4.10</t>
+          <t>6.4.11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EPR_Mode Message</t>
+          <t>Source_Info Message</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11474</v>
+        <v>4285</v>
       </c>
       <c r="D106" t="b">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>2069</v>
+        <v>698</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6.4.11</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Source_Info Message</t>
+          <t>Extended Message</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4285</v>
+        <v>2509</v>
       </c>
       <c r="D107" t="b">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>698</v>
+        <v>407</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5.1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Extended Message</t>
+          <t>Source_Capabilities_Extended Message</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2509</v>
+        <v>9796</v>
       </c>
       <c r="D108" t="b">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>407</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6.5.1</t>
+          <t>6.5.2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Source_Capabilities_Extended Message</t>
+          <t>Status Message</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9796</v>
+        <v>9219</v>
       </c>
       <c r="D109" t="b">
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>1724</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6.5.2</t>
+          <t>6.5.3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Status Message</t>
+          <t>Get_Battery_Cap Message</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9219</v>
+        <v>0</v>
       </c>
       <c r="D110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>1610</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6.5.3</t>
+          <t>6.5.4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Get_Battery_Cap Message</t>
+          <t>Get_Battery_Status Message</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="D111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6.5.4</t>
+          <t>6.5.5</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Get_Battery_Status Message</t>
+          <t>Battery_Capabilities Message</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2080</v>
+        <v>3041</v>
       </c>
       <c r="D112" t="b">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>310</v>
+        <v>496</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6.5.5</t>
+          <t>6.5.6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Battery_Capabilities Message</t>
+          <t>Get_Manufacturer_Info Message</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3041</v>
+        <v>1511</v>
       </c>
       <c r="D113" t="b">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>496</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6.5.6</t>
+          <t>6.5.7</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Get_Manufacturer_Info Message</t>
+          <t>Manufacturer_Info Message</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1511</v>
+        <v>3249</v>
       </c>
       <c r="D114" t="b">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>228</v>
+        <v>532</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6.5.7</t>
+          <t>6.5.8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Manufacturer_Info Message</t>
+          <t>Security Messages</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3249</v>
+        <v>2217</v>
       </c>
       <c r="D115" t="b">
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>532</v>
+        <v>357</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6.5.8</t>
+          <t>6.5.9</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Security Messages</t>
+          <t>Firmware Update Messages</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2217</v>
+        <v>1317</v>
       </c>
       <c r="D116" t="b">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>357</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6.5.9</t>
+          <t>6.5.10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Firmware Update Messages</t>
+          <t>PPS_Status Message</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1317</v>
+        <v>2911</v>
       </c>
       <c r="D117" t="b">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>189</v>
+        <v>491</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6.5.10</t>
+          <t>6.5.11</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PPS_Status Message</t>
+          <t>Country_Codes Message</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2911</v>
+        <v>1283</v>
       </c>
       <c r="D118" t="b">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>491</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6.5.11</t>
+          <t>6.5.12</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Country_Codes Message</t>
+          <t>Country_Info Message</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1283</v>
+        <v>1447</v>
       </c>
       <c r="D119" t="b">
         <v>1</v>
@@ -10353,117 +10353,117 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>6.5.12</t>
+          <t>6.5.13</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Country_Info Message</t>
+          <t>Sink_Capabilities_Extended Message</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1447</v>
+        <v>13482</v>
       </c>
       <c r="D120" t="b">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>211</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6.5.13</t>
+          <t>6.5.14</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sink_Capabilities_Extended Message</t>
+          <t>Extended_Control Message</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>13482</v>
+        <v>2733</v>
       </c>
       <c r="D121" t="b">
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>2368</v>
+        <v>421</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6.5.14</t>
+          <t>6.5.15</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Extended_Control Message</t>
+          <t>EPR Capabilities Message</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2733</v>
+        <v>5326</v>
       </c>
       <c r="D122" t="b">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>421</v>
+        <v>913</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6.5.15</t>
+          <t>6.5.16</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EPR Capabilities Message</t>
+          <t>Vendor_Defined_Extended Message</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5326</v>
+        <v>3047</v>
       </c>
       <c r="D123" t="b">
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>913</v>
+        <v>515</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6.5.16</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vendor_Defined_Extended Message</t>
+          <t>Timers</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3047</v>
+        <v>0</v>
       </c>
       <c r="D124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.6.1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers</t>
+          <t>CRCReceiveTimer</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -10479,12 +10479,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6.6.1</t>
+          <t>6.6.2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CRCReceiveTimer</t>
+          <t>SenderResponseTimer</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -10500,138 +10500,138 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6.6.2</t>
+          <t>6.6.3</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SenderResponseTimer</t>
+          <t>Capability Timers</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>6670</v>
       </c>
       <c r="D127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6.6.3</t>
+          <t>6.6.4</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capability Timers</t>
+          <t>Wait Timers and Times</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6670</v>
+        <v>0</v>
       </c>
       <c r="D128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6.6.4</t>
+          <t>6.6.5</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Wait Timers and Times</t>
+          <t>Power Supply Timers</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>6826</v>
       </c>
       <c r="D129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6.6.5</t>
+          <t>6.6.6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Power Supply Timers</t>
+          <t>NoResponseTimer</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6826</v>
+        <v>0</v>
       </c>
       <c r="D130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>1106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6.6.6</t>
+          <t>6.6.7</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NoResponseTimer</t>
+          <t>BIST Timers</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2806</v>
       </c>
       <c r="D131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6.6.7</t>
+          <t>6.6.8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BIST Timers</t>
+          <t>Power Role Swap Timers</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2806</v>
+        <v>0</v>
       </c>
       <c r="D132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6.6.10</t>
+          <t>6.6.9</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Data Reset Timers</t>
+          <t>Soft Reset Timers</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -10647,96 +10647,96 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6.6.8</t>
+          <t>6.6.10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Power Role Swap Timers</t>
+          <t>Data Reset Timers</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>3340</v>
       </c>
       <c r="D134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6.6.9</t>
+          <t>6.6.11</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Soft Reset Timers</t>
+          <t>Hard Reset Timers</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3340</v>
+        <v>0</v>
       </c>
       <c r="D135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6.6.11</t>
+          <t>6.6.12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hard Reset Timers</t>
+          <t>Structured VDM Timers</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>6852</v>
       </c>
       <c r="D136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6.6.12</t>
+          <t>6.6.13</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Structured VDM Timers</t>
+          <t>VCONN Timers</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>6852</v>
+        <v>0</v>
       </c>
       <c r="D137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>1056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6.6.13</t>
+          <t>6.6.14</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VCONN Timers</t>
+          <t>tCableMessage</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -10752,12 +10752,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6.6.14</t>
+          <t>6.6.15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>tCableMessage</t>
+          <t>DiscoverIdentityTimer</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -10773,180 +10773,180 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6.6.15</t>
+          <t>6.6.16</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DiscoverIdentityTimer</t>
+          <t>Collision Avoidance Timers</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>2473</v>
       </c>
       <c r="D140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6.6.16</t>
+          <t>6.6.17</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Collision Avoidance Timers</t>
+          <t>Fast Role Swap Timers</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2473</v>
+        <v>0</v>
       </c>
       <c r="D141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6.6.17</t>
+          <t>6.6.18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Fast Role Swap Timers</t>
+          <t>Chunking Timers</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>2595</v>
       </c>
       <c r="D142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6.6.18</t>
+          <t>6.6.19</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Chunking Timers</t>
+          <t>Programmable Power Supply Timers</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2595</v>
+        <v>3295</v>
       </c>
       <c r="D143" t="b">
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>395</v>
+        <v>512</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>6.6.19</t>
+          <t>6.6.20</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Programmable Power Supply Timers</t>
+          <t>tEnterUSB</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3295</v>
+        <v>0</v>
       </c>
       <c r="D144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6.6.20</t>
+          <t>6.6.21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>tEnterUSB</t>
+          <t>EPR Timers</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>4243</v>
       </c>
       <c r="D145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6.6.21</t>
+          <t>6.6.22</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EPR Timers</t>
+          <t>Time Values and Timers</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4243</v>
+        <v>5240</v>
       </c>
       <c r="D146" t="b">
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>677</v>
+        <v>653</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6.6.22</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Time Values and Timers</t>
+          <t>Counters</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5240</v>
+        <v>0</v>
       </c>
       <c r="D147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.7.1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Counters</t>
+          <t>MessageID Counter</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -10962,54 +10962,54 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6.7.1</t>
+          <t>6.7.2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MessageID Counter</t>
+          <t>Retry Counter</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>2905</v>
       </c>
       <c r="D149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>6.7.2</t>
+          <t>6.7.3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Retry Counter</t>
+          <t>Hard Reset Counter</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2905</v>
+        <v>0</v>
       </c>
       <c r="D150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6.7.3</t>
+          <t>6.7.4</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hard Reset Counter</t>
+          <t>Capabilities Counter</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -11025,12 +11025,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6.7.4</t>
+          <t>6.7.5</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Capabilities Counter</t>
+          <t>Discover Identity Counter</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -11046,516 +11046,516 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6.7.5</t>
+          <t>6.7.6</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Discover Identity Counter</t>
+          <t>VDMBusyCounter</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>2601</v>
       </c>
       <c r="D153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6.7.6</t>
+          <t>6.7.7</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VDMBusyCounter</t>
+          <t>Counter Values and Counters</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2601</v>
+        <v>721</v>
       </c>
       <c r="D154" t="b">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>389</v>
+        <v>81</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6.7.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Counter Values and Counters</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>721</v>
+        <v>0</v>
       </c>
       <c r="D155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.8.1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Soft Reset and Protocol Error</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>4382</v>
       </c>
       <c r="D156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>667</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6.8.1</t>
+          <t>6.8.2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Soft Reset and Protocol Error</t>
+          <t>Data Reset</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4382</v>
+        <v>0</v>
       </c>
       <c r="D157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6.8.2</t>
+          <t>6.8.3</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Data Reset</t>
+          <t>Hard Reset</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>3347</v>
       </c>
       <c r="D158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>6.8.3</t>
+          <t>6.8.4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hard Reset</t>
+          <t>Cable Reset</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3347</v>
+        <v>1928</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>566</v>
+        <v>334</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6.8.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Cable Reset</t>
+          <t>Accept, Reject and Wait</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1928</v>
+        <v>629</v>
       </c>
       <c r="D160" t="b">
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>334</v>
+        <v>102</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Accept, Reject and Wait</t>
+          <t>Collision Avoidance</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>629</v>
+        <v>1002</v>
       </c>
       <c r="D161" t="b">
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Collision Avoidance</t>
+          <t>Message Discarding</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1002</v>
+        <v>1045</v>
       </c>
       <c r="D162" t="b">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Message Discarding</t>
+          <t>State behavior</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1045</v>
+        <v>0</v>
       </c>
       <c r="D163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.12.1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>State behavior</t>
+          <t>Introduction to state diagrams used in Chapter 6</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>2034</v>
       </c>
       <c r="D164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>6.12.1</t>
+          <t>6.12.2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Introduction to state diagrams used in Chapter 6</t>
+          <t>State Operation</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2034</v>
+        <v>45387</v>
       </c>
       <c r="D165" t="b">
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>352</v>
+        <v>7479</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6.12.2</t>
+          <t>6.12.3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>State Operation</t>
+          <t>List of Protocol Layer States</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>45387</v>
+        <v>2601</v>
       </c>
       <c r="D166" t="b">
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>7479</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6.12.3</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>List of Protocol Layer States</t>
+          <t>Message Applicability</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2601</v>
+        <v>1892</v>
       </c>
       <c r="D167" t="b">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>200</v>
+        <v>317</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.13.1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Message Applicability</t>
+          <t>Applicability of Control Messages</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1892</v>
+        <v>3468</v>
       </c>
       <c r="D168" t="b">
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>317</v>
+        <v>688</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6.13.1</t>
+          <t>6.13.2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Applicability of Control Messages</t>
+          <t>Applicability of Data Messages</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3468</v>
+        <v>3197</v>
       </c>
       <c r="D169" t="b">
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>688</v>
+        <v>617</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6.13.2</t>
+          <t>6.13.3</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Applicability of Data Messages</t>
+          <t>Applicability of Extended Messages</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3197</v>
+        <v>6129</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>617</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6.13.3</t>
+          <t>6.13.4</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Applicability of Extended Messages</t>
+          <t>Applicability of Extended Control Messages</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>6129</v>
+        <v>1011</v>
       </c>
       <c r="D171" t="b">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>1059</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6.13.4</t>
+          <t>6.13.5</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Applicability of Extended Control Messages</t>
+          <t>Applicability of Structured VDM Commands</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1011</v>
+        <v>1656</v>
       </c>
       <c r="D172" t="b">
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>178</v>
+        <v>325</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>6.13.5</t>
+          <t>6.13.6</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Applicability of Structured VDM Commands</t>
+          <t>Applicability of Reset Signaling</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1656</v>
+        <v>0</v>
       </c>
       <c r="D173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6.13.6</t>
+          <t>6.13.7</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Applicability of Reset Signaling</t>
+          <t>Applicability of Fast Role Swap Request</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="D174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6.13.7</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Applicability of Fast Role Swap Request</t>
+          <t>Value Parameters</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1163</v>
+        <v>508</v>
       </c>
       <c r="D175" t="b">
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>208</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Value Parameters</t>
+          <t>Power Supply. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="D176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Power Supply. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>Source Requirements</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -11571,12 +11571,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1.1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Source Requirements</t>
+          <t>Behavioral Aspects</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -11592,12 +11592,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>7.1.1</t>
+          <t>7.1.2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Behavioral Aspects</t>
+          <t>Source Bulk Capacitance</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -11613,148 +11613,148 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>7.1.3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Source Bulk Capacitance</t>
+          <t>Types of Sources</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>2484</v>
       </c>
       <c r="D180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>7.1.3</t>
+          <t>7.1.4</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Types of Sources</t>
+          <t>Source Transitions</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2484</v>
+        <v>20892</v>
       </c>
       <c r="D181" t="b">
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>388</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7.1.4</t>
+          <t>7.1.5</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Source Transitions</t>
+          <t>Response to Hard Resets</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>20892</v>
+        <v>2459</v>
       </c>
       <c r="D182" t="b">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>3205</v>
+        <v>414</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>7.1.5</t>
+          <t>7.1.6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Response to Hard Resets</t>
+          <t>Changing the Output Power Capability</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2459</v>
+        <v>0</v>
       </c>
       <c r="D183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7.1.6</t>
+          <t>7.1.7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Changing the Output Power Capability</t>
+          <t>Robust Source Operation</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>6710</v>
       </c>
       <c r="D184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7.1.7</t>
+          <t>7.1.8</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Robust Source Operation</t>
+          <t>Output Voltage Tolerance and Range</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6710</v>
+        <v>5262</v>
       </c>
       <c r="D185" t="b">
         <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>1039</v>
+        <v>799</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>7.1.8</t>
+          <t>7.1.9</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Output Voltage Tolerance and Range</t>
+          <t>Charging and Discharging the Bulk Capacitance on VBUS</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>5262</v>
+        <v>0</v>
       </c>
       <c r="D186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -11790,129 +11790,129 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>2628</v>
       </c>
       <c r="D188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>7.1.9</t>
+          <t>7.1.12</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Charging and Discharging the Bulk Capacitance on VBUS</t>
+          <t>Source Capabilities Extended Parameters</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2628</v>
+        <v>4355</v>
       </c>
       <c r="D189" t="b">
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>420</v>
+        <v>674</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7.1.12</t>
+          <t>7.1.13</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Source Capabilities Extended Parameters</t>
+          <t>Fast Role Swap</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>4355</v>
+        <v>3555</v>
       </c>
       <c r="D190" t="b">
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>674</v>
+        <v>604</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7.1.13</t>
+          <t>7.1.14</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fast Role Swap</t>
+          <t>Non-application of VBUS Slew Rate Limits</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3555</v>
+        <v>2256</v>
       </c>
       <c r="D191" t="b">
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>604</v>
+        <v>386</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7.1.14</t>
+          <t>7.1.15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Non-application of VBUS Slew Rate Limits</t>
+          <t>VCONN Power Cycle</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2256</v>
+        <v>2716</v>
       </c>
       <c r="D192" t="b">
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>386</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7.1.15</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VCONN Power Cycle</t>
+          <t>Sink Requirements</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2716</v>
+        <v>0</v>
       </c>
       <c r="D193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.2.1</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Sink Requirements</t>
+          <t>Behavioral Aspects</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -11928,12 +11928,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t>7.2.2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Behavioral Aspects</t>
+          <t>Sink Bulk Capacitance</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -11949,54 +11949,54 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7.2.2</t>
+          <t>7.2.3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sink Bulk Capacitance</t>
+          <t>Sink Standby</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>2853</v>
       </c>
       <c r="D196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>7.2.3</t>
+          <t>7.2.4</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sink Standby</t>
+          <t>Suspend Power Consumption</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2853</v>
+        <v>0</v>
       </c>
       <c r="D197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7.2.4</t>
+          <t>7.2.5</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Suspend Power Consumption</t>
+          <t>Zero Negotiated Current</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -12012,12 +12012,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7.2.5</t>
+          <t>7.2.6</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Zero Negotiated Current</t>
+          <t>Transient Load Behavior</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -12033,12 +12033,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>7.2.6</t>
+          <t>7.2.7</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Transient Load Behavior</t>
+          <t>Swap Standby for Sinks</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -12054,904 +12054,904 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>7.2.7</t>
+          <t>7.2.8</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Swap Standby for Sinks</t>
+          <t>Sink Peak Current Operation</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="D201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>687</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>7.2.8</t>
+          <t>7.2.9</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Sink Peak Current Operation</t>
+          <t>Robust Sink Operation</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4157</v>
+        <v>4051</v>
       </c>
       <c r="D202" t="b">
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>687</v>
+        <v>656</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7.2.9</t>
+          <t>7.2.10</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Robust Sink Operation</t>
+          <t>Fast Role Swap</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>4051</v>
+        <v>4176</v>
       </c>
       <c r="D203" t="b">
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>656</v>
+        <v>679</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7.2.10</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Fast Role Swap</t>
+          <t>Transitions</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4176</v>
+        <v>1940</v>
       </c>
       <c r="D204" t="b">
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>679</v>
+        <v>388</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.3.1</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Transitions</t>
+          <t>Transitions caused by a Request Message</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1940</v>
+        <v>55505</v>
       </c>
       <c r="D205" t="b">
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>388</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>7.3.1</t>
+          <t>7.3.2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Transitions caused by a Request Message</t>
+          <t>Transitions Caused by Power Role Swap</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>55505</v>
+        <v>11310</v>
       </c>
       <c r="D206" t="b">
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>8695</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>7.3.2</t>
+          <t>7.3.3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Transitions Caused by Power Role Swap</t>
+          <t>Transitions Caused by Hard Reset</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>11310</v>
+        <v>4695</v>
       </c>
       <c r="D207" t="b">
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>2021</v>
+        <v>788</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>7.3.3</t>
+          <t>7.3.4</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Transitions Caused by Hard Reset</t>
+          <t>Transitions Caused by Fast Role Swap</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4695</v>
+        <v>5137</v>
       </c>
       <c r="D208" t="b">
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>788</v>
+        <v>928</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>7.3.4</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Transitions Caused by Fast Role Swap</t>
+          <t>Electrical Parameters</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>5137</v>
+        <v>0</v>
       </c>
       <c r="D209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4.1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Electrical Parameters</t>
+          <t>Source Electrical Parameters</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0</v>
+        <v>11530</v>
       </c>
       <c r="D210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7.4.1</t>
+          <t>7.4.2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Source Electrical Parameters</t>
+          <t>Sink Electrical Parameters</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>11530</v>
+        <v>3277</v>
       </c>
       <c r="D211" t="b">
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>1818</v>
+        <v>536</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>7.4.2</t>
+          <t>7.4.3</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Sink Electrical Parameters</t>
+          <t>Common Electrical Parameters</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3277</v>
+        <v>1327</v>
       </c>
       <c r="D212" t="b">
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>536</v>
+        <v>212</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7.4.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Common Electrical Parameters</t>
+          <t>Device Policy . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="D213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Device Policy . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="D214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Device Policy Manager</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>266</v>
+        <v>4413</v>
       </c>
       <c r="D215" t="b">
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>42</v>
+        <v>725</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.2.1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Device Policy Manager</t>
+          <t>Capabilities</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>4413</v>
+        <v>0</v>
       </c>
       <c r="D216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8.2.1</t>
+          <t>8.2.2</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Capabilities</t>
+          <t>System Policy</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>3445</v>
       </c>
       <c r="D217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8.2.2</t>
+          <t>8.2.3</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>System Policy</t>
+          <t>Control of Source/Sink</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="D218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8.2.3</t>
+          <t>8.2.4</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Control of Source/Sink</t>
+          <t>Cable Detection</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="D219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8.2.4</t>
+          <t>8.2.5</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Cable Detection</t>
+          <t>Managing Power Requirements</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2664</v>
+        <v>4047</v>
       </c>
       <c r="D220" t="b">
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>425</v>
+        <v>645</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8.2.5</t>
+          <t>8.2.6</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Managing Power Requirements</t>
+          <t>Use of "Unconstrained Power" bit with Batteries and AC supplies</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>4047</v>
+        <v>6677</v>
       </c>
       <c r="D221" t="b">
         <v>1</v>
       </c>
       <c r="E221" t="n">
-        <v>645</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>8.2.6</t>
+          <t>8.2.7</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Use of "Unconstrained Power" bit with Batteries and AC supplies</t>
+          <t>Interface to the Policy Engine</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>6677</v>
+        <v>2446</v>
       </c>
       <c r="D222" t="b">
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>1091</v>
+        <v>373</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>8.2.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Interface to the Policy Engine</t>
+          <t>Policy Engine</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2446</v>
+        <v>0</v>
       </c>
       <c r="D223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.3.1</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Policy Engine</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="D224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8.3.1</t>
+          <t>8.3.2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Atomic Message Sequence Diagrams</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>336</v>
+        <v>614496</v>
       </c>
       <c r="D225" t="b">
         <v>1</v>
       </c>
       <c r="E225" t="n">
-        <v>55</v>
+        <v>99765</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8.3.2</t>
+          <t>8.3.3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Atomic Message Sequence Diagrams</t>
+          <t>State Diagrams</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>614496</v>
+        <v>249408</v>
       </c>
       <c r="D226" t="b">
         <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>99765</v>
+        <v>38749</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>8.3.3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>State Diagrams</t>
+          <t>States and Status Reporting . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>249408</v>
+        <v>0</v>
       </c>
       <c r="D227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>38749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>States and Status Reporting . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>4725</v>
       </c>
       <c r="D228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.1.1</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>PDUSB Device and Hub Requirements</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>4725</v>
+        <v>410</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>780</v>
+        <v>66</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>9.1.1</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PDUSB Device and Hub Requirements</t>
+          <t>Mapping to USB Device States</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>410</v>
+        <v>3233</v>
       </c>
       <c r="D230" t="b">
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>66</v>
+        <v>559</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>9.1.3</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mapping to USB Device States</t>
+          <t>PD Software Stack</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3233</v>
+        <v>583</v>
       </c>
       <c r="D231" t="b">
         <v>1</v>
       </c>
       <c r="E231" t="n">
-        <v>559</v>
+        <v>101</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>9.1.3</t>
+          <t>9.1.4</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PD Software Stack</t>
+          <t>PDUSB Device Enumeration</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>583</v>
+        <v>1671</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>101</v>
+        <v>270</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>9.1.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PDUSB Device Enumeration</t>
+          <t>PD Specific Descriptors</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1671</v>
+        <v>745</v>
       </c>
       <c r="D233" t="b">
         <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>270</v>
+        <v>124</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.2.1</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PD Specific Descriptors</t>
+          <t>USB Power Delivery Capability Descriptor</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>745</v>
+        <v>2206</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
       </c>
       <c r="E234" t="n">
-        <v>124</v>
+        <v>396</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>9.2.1</t>
+          <t>9.2.2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>USB Power Delivery Capability Descriptor</t>
+          <t>Battery Info Capability Descriptor</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2206</v>
+        <v>2352</v>
       </c>
       <c r="D235" t="b">
         <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>396</v>
+        <v>367</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>9.2.2</t>
+          <t>9.2.3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Battery Info Capability Descriptor</t>
+          <t>PD Consumer Port Capability Descriptor</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2352</v>
+        <v>1559</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>367</v>
+        <v>255</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>9.2.3</t>
+          <t>9.2.4</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PD Consumer Port Capability Descriptor</t>
+          <t>PD Provider Port Capability Descriptor</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1559</v>
+        <v>1303</v>
       </c>
       <c r="D237" t="b">
         <v>1</v>
       </c>
       <c r="E237" t="n">
-        <v>255</v>
+        <v>216</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>9.2.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PD Provider Port Capability Descriptor</t>
+          <t>PD Specific Requests and Events</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1303</v>
+        <v>0</v>
       </c>
       <c r="D238" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.3.1</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PD Specific Requests and Events</t>
+          <t>PD Specific Requests</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>1367</v>
       </c>
       <c r="D239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9.3.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PD Specific Requests</t>
+          <t>PDUSB Hub and PDUSB Peripheral Device Requests</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1367</v>
+        <v>0</v>
       </c>
       <c r="D240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.4.1</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PDUSB Hub and PDUSB Peripheral Device Requests</t>
+          <t>GetBatteryStatus</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>0</v>
+        <v>1287</v>
       </c>
       <c r="D241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>9.4.1</t>
+          <t>9.4.2</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>GetBatteryStatus</t>
+          <t>SetPDFeature</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1287</v>
+        <v>0</v>
       </c>
       <c r="D242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E242" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>9.4.2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SetPDFeature</t>
+          <t>UPnoivweresarl SReurilael sB u. s. P. o. w. e. r. D. .e l.i v. e. r.y . S.p .e .c i.f i. c.a .t i.o .n ., R. .e v. i.s i.o .n . 3. ..2 ., V. e. r.s .i o. n. 1. ..1 ., 2. 0. 2. 4. -.1 .0 . . . . . 9P9a5ge</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5017</v>
+        <v>1797860</v>
       </c>
       <c r="D243" t="b">
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>829</v>
+        <v>281417</v>
       </c>
     </row>
     <row r="244">
